--- a/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -557,12 +554,61 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 밤에 먹는 것 때문에 문제가 있어서 왔어요. 혼자 있을 때 먹기 시작하면, 뭔가가 저를 장악하는 것 같은 느낌이 들고, 멈출 수가 없어요. 스스로 음식을 치우라고 말해도 소용이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 먹고 난 후에, 일부러 토를 하시거나 음식을 없애거나 체중이 느는 걸 막으려고 다른 행동을 하시는 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 그렇게 먹고 나면 보통 화장실에 가서 일부러 토를 해요. 그게 되돌릴 수 있는 유일한 방법처럼 느껴져요, 칼로리가 진짜로... 몸에 쌓이기 전에요, 그런 느낌이랄까요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 폭식증 (D022)
 인구통계: 성별 남성 / 나이 33 / 직업상태 animal caretaker / 최종학력 학사
@@ -571,128 +617,39 @@
 증상 지속 기간: 5 months
 추가 요건: The binge eating and inappropriate compensatory behaviors both occur, on average, at least once a week for 3 months
 주호소 증상 코드: S050
-배경 서술: Agustín은 배우자와 별거한 후 함께 살던 Evergreen Park의 집에서 야생동물 구조센터 근처의 더 작은 아파트로 이사했고, 요리나 축구, 밤늦게 기타를 치던 일상의 루틴이 흔들리기 시작했다. 처음에는 이 전환기 동안 안정감을 유지하기 위해 식사와 운동을 엄격하게 통제하려 했지만, 이후 다섯 달에 걸쳐 체중이 늘까 봐 두려워하는 마음과 자신의 체형에 대한 가혹한 자기 평가가 커져갔고, 저녁 근무를 마치고 혼자 있을 때 평소와 달리 지나치게 많은 양을 먹는 일이 반복되었다. 그는 이후 스스로 통제력을 잃었다고 느낀 것을 되돌리기 위해 구토를 하기 시작했고, 이를 체계적인 업무 이미지와 지역사회 활동 뒤에 숨겼다. 이중언어 아웃리치 발표 도중 언제 자리를 뜰 수 있을지, 그리고 앞서 먹은 것을 어떻게 만회할지에 정신이 팔려 발표를 망친 후, 그는 결국 직접 직원 지원 프로그램에 연락해 정신건강의학과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 밤에 먹는 것 때문에 문제가 있어서 왔어요. 혼자 있을 때 먹기 시작하면, 뭔가가 저를 장악하는 것 같은 느낌이 들고, 멈출 수가 없어요. 스스로 음식을 치우라고 말해도 소용이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 먹고 난 후에, 일부러 토를 하시거나 음식을 없애거나 체중이 느는 걸 막으려고 다른 행동을 하시는 게 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 그렇게 먹고 나면 보통 화장실에 가서 일부러 토를 해요. 그게 되돌릴 수 있는 유일한 방법처럼 느껴져요, 칼로리가 진짜로... 몸에 쌓이기 전에요, 그런 느낌이랄까요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+배경 서술: Agustín은 배우자와 별거한 후 함께 살던 Evergreen Park의 집에서 야생동물 구조센터 근처의 더 작은 아파트로 이사했고, 요리나 축구, 밤늦게 기타를 치던 일상의 루틴이 흔들리기 시작했다. 처음에는 이 전환기 동안 안정감을 유지하기 위해 식사와 운동을 엄격하게 통제하려 했지만, 이후 다섯 달에 걸쳐 체중이 늘까 봐 두려워하는 마음과 자신의 체형에 대한 가혹한 자기 평가가 커져갔고, 저녁 근무를 마치고 혼자 있을 때 평소와 달리 지나치게 많은 양을 먹는 일이 반복되었다. 그는 이후 스스로 통제력을 잃었다고 느낀 것을 되돌리기 위해 구토를 하기 시작했고, 이를 체계적인 업무 이미지와 지역사회 활동 뒤에 숨겼다. 이중언어 아웃리치 발표 도중 언제 자리를 뜰 수 있을지, 그리고 앞서 먹은 것을 어떻게 만회할지에 정신이 팔려 발표를 망친 후, 그는 결국 직접 직원 지원 프로그램에 연락해 정신건강의학과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S048 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
+        </is>
+      </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
-  누락: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
-  누락: 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.; 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
+          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)
+지속 기간 요건: 없음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
@@ -603,6 +603,11 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -645,11 +650,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -501,7 +502,9 @@
           <t>정보습득점수 IAS (턴 평균)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -551,6 +554,7 @@
         <v>0.1111</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
